--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828BDCE0-292F-4FC8-8C58-7DF805EB5A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A387E5-37C4-4D76-9D89-8E1476BAD962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
@@ -531,7 +531,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -556,6 +556,13 @@
     </font>
     <font>
       <sz val="6"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
@@ -605,11 +612,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -621,17 +625,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2093,386 +2103,386 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FE30FC-11F3-410C-9482-0A4C3F5D7DD0}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="11" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.58203125" style="1"/>
-    <col min="2" max="2" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.08203125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="2.58203125" style="1"/>
+    <col min="1" max="1" width="2.58203125" style="4"/>
+    <col min="2" max="2" width="3.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.58203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.08203125" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="2.58203125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <v>1</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="7">
         <v>46158</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>46158</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>46158</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>46158</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>46158</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>46166</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <v>4</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>46158</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>46166</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="5">
+    <row r="7" spans="1:6" ht="22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="6">
         <v>5</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>46166</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>46167</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="5">
+      <c r="B8" s="6">
         <v>6</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>46167</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>46167</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="5">
+    <row r="9" spans="1:6" ht="22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="6">
         <v>7</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>46166</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>46180</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="5">
+      <c r="B10" s="6">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>46166</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>46186</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>46166</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="5">
+      <c r="B12" s="6">
         <v>10</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>46166</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>46180</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="27" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="5">
+    <row r="13" spans="1:6" ht="22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="6">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>46186</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>46200</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="5">
+      <c r="B14" s="6">
         <v>12</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>46166</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>46208</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="67.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="5">
+    <row r="15" spans="1:6" ht="55" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="6">
         <v>13</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>46208</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>46208</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="121.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="5">
+    <row r="16" spans="1:6" ht="99" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="6">
         <v>14</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>46208</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="6"/>
+      <c r="F16" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="94.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="5">
+    <row r="17" spans="2:5" ht="77" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="6">
         <v>15</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>46208</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="2:5" ht="81" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="5">
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="2:5" ht="66" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="6">
         <v>16</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
         <v>46208</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="2:5" ht="81" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="5">
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="2:5" ht="66" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="6">
         <v>17</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="7">
         <v>46208</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="2:5" ht="81" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="5">
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="2:5" ht="66" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="6">
         <v>18</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
         <v>46208</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="2:5" ht="67.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="5">
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="2:5" ht="55" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="6">
         <v>19</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="7">
         <v>46208</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="5">
+      <c r="B22" s="6">
         <v>20</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="5">
+      <c r="B23" s="6">
         <v>21</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="5">
+      <c r="B24" s="6">
         <v>22</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="5">
+      <c r="B25" s="6">
         <v>23</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="5">
+      <c r="B26" s="6">
         <v>24</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="5">
+      <c r="B27" s="6">
         <v>25</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="5">
+      <c r="B28" s="6">
         <v>26</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="5">
+      <c r="B29" s="6">
         <v>27</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="5">
+      <c r="B30" s="6">
         <v>28</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="5">
+      <c r="B31" s="6">
         <v>29</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="5">
+      <c r="B32" s="6">
         <v>30</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -2487,44 +2497,44 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="2.58203125" style="2"/>
-    <col min="3" max="3" width="18.4140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.9140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="2.58203125" style="2"/>
+    <col min="1" max="2" width="2.58203125" style="1"/>
+    <col min="3" max="3" width="18.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="2.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="368" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
